--- a/Stocks/IESC.xlsx
+++ b/Stocks/IESC.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://academiafaedupt-my.sharepoint.com/personal/sbclemente_academiafa_edu_pt/Documents/Gigs/WorkingFolder/Finance_Shared/Stocks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="189" documentId="8_{E883A8EF-561B-4C2B-9534-AAE527A24DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E0690CC-8B8D-49E2-87AE-3666B6D45206}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="8_{E883A8EF-561B-4C2B-9534-AAE527A24DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A29A330F-B7CA-4527-B29D-23EA26CE881B}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{C2872281-F2D6-482A-824F-432F6AC9B63B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C2872281-F2D6-482A-824F-432F6AC9B63B}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
     <sheet name="model " sheetId="2" r:id="rId2"/>
+    <sheet name="Folha1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="81">
   <si>
     <t>Price</t>
   </si>
@@ -232,6 +233,57 @@
   </si>
   <si>
     <t>Reported NI</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>Contigent</t>
+  </si>
+  <si>
+    <t>OPEX</t>
+  </si>
+  <si>
+    <t>PRETAX</t>
+  </si>
+  <si>
+    <t>Tac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPS </t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Q127</t>
+  </si>
+  <si>
+    <t>Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential </t>
+  </si>
+  <si>
+    <t>Comercial  &amp; Industrial</t>
+  </si>
+  <si>
+    <t>Infra solutions</t>
+  </si>
+  <si>
+    <t>VAL</t>
+  </si>
+  <si>
+    <t>PS</t>
   </si>
 </sst>
 </file>
@@ -276,10 +328,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -299,6 +350,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -682,590 +737,218 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B14CCB7-C163-4ACC-99B1-05CB79F3A6D9}">
-  <dimension ref="B2:AV56"/>
+  <dimension ref="B6:AV64"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="25" max="25" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
+    <row r="6" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F6" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G6" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H6" t="s">
         <v>7</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I6" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J6" t="s">
         <v>13</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K6" t="s">
         <v>14</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L6" t="s">
         <v>15</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M6" t="s">
         <v>16</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N6" t="s">
         <v>17</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O6" t="s">
         <v>18</v>
       </c>
-      <c r="U2">
+      <c r="P6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>72</v>
+      </c>
+      <c r="R6" t="s">
+        <v>73</v>
+      </c>
+      <c r="S6" t="s">
+        <v>74</v>
+      </c>
+      <c r="U6">
         <v>2022</v>
       </c>
-      <c r="V2">
-        <f>+U2+1</f>
+      <c r="V6">
+        <f>+U6+1</f>
         <v>2023</v>
       </c>
-      <c r="W2">
-        <f t="shared" ref="W2:AF2" si="0">+V2+1</f>
+      <c r="W6">
+        <f t="shared" ref="W6:AF6" si="0">+V6+1</f>
         <v>2024</v>
       </c>
-      <c r="X2">
+      <c r="X6">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="Y2">
+      <c r="Y6">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="Z2">
+      <c r="Z6">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="AA2">
+      <c r="AA6">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="AB2">
+      <c r="AB6">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="AC2">
+      <c r="AC6">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="AD2">
+      <c r="AD6">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
-      <c r="AE2">
+      <c r="AE6">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="AF2">
+      <c r="AF6">
         <f t="shared" si="0"/>
         <v>2033</v>
       </c>
     </row>
-    <row r="3" spans="2:48" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="2:32" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="K11" s="4">
         <v>775.8</v>
       </c>
-      <c r="K3" s="5">
+      <c r="L11" s="4">
         <v>749.5</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5">
+      <c r="M11" s="4">
+        <v>890</v>
+      </c>
+      <c r="N11" s="4">
+        <v>897</v>
+      </c>
+      <c r="O11" s="4">
         <v>897.8</v>
       </c>
-      <c r="O3" s="5">
+      <c r="P11" s="4">
         <v>871</v>
       </c>
-      <c r="U3" s="4">
+      <c r="Q11" s="3">
+        <v>1243</v>
+      </c>
+      <c r="U11" s="3">
         <v>2166</v>
       </c>
-      <c r="V3" s="4">
+      <c r="V11" s="3">
         <v>2377.1999999999998</v>
       </c>
-      <c r="W3" s="4">
+      <c r="W11" s="3">
         <v>3371.5</v>
       </c>
     </row>
-    <row r="4" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="K12" s="1">
         <v>589.4</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L12" s="1">
         <v>571.5</v>
       </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1">
+      <c r="M12" s="1">
+        <v>650</v>
+      </c>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1">
         <v>664.8</v>
       </c>
-      <c r="O4" s="1">
+      <c r="P12" s="1">
         <v>651</v>
       </c>
-      <c r="U4">
+      <c r="Q12" s="1">
+        <v>902</v>
+      </c>
+      <c r="U12">
         <v>1847.9</v>
       </c>
-      <c r="V4">
+      <c r="V12">
         <v>1932</v>
       </c>
-      <c r="W4">
+      <c r="W12">
         <v>2512</v>
       </c>
     </row>
-    <row r="5" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1">
-        <f>+J3-J4</f>
-        <v>186.39999999999998</v>
-      </c>
-      <c r="K5" s="1">
-        <f>+K3-K4</f>
-        <v>178</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1">
-        <f>+N3-N4</f>
-        <v>233</v>
-      </c>
-      <c r="O5" s="1">
-        <f>+O3-O4</f>
-        <v>220</v>
-      </c>
-      <c r="U5">
-        <f t="shared" ref="U5:V5" si="1">+U3-U4</f>
-        <v>318.09999999999991</v>
-      </c>
-      <c r="V5">
-        <f t="shared" si="1"/>
-        <v>445.19999999999982</v>
-      </c>
-      <c r="W5">
-        <f>+W3-W4</f>
-        <v>859.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1">
-        <v>110.9</v>
-      </c>
-      <c r="K6" s="1">
-        <v>103</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1">
-        <v>128.6</v>
-      </c>
-      <c r="O6" s="1">
-        <v>121.8</v>
-      </c>
-      <c r="U6">
-        <v>262.7</v>
-      </c>
-      <c r="V6">
-        <v>298.60000000000002</v>
-      </c>
-      <c r="W6">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="7" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1">
-        <f>+J5-J6</f>
-        <v>75.499999999999972</v>
-      </c>
-      <c r="K7" s="1">
-        <f>+K5-K6</f>
-        <v>75</v>
-      </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1">
-        <f>+N5-N6</f>
-        <v>104.4</v>
-      </c>
-      <c r="O7" s="1">
-        <f>+O5-O6</f>
-        <v>98.2</v>
-      </c>
-      <c r="U7">
-        <f t="shared" ref="U7:V7" si="2">+U5-U6</f>
-        <v>55.39999999999992</v>
-      </c>
-      <c r="V7">
-        <f t="shared" si="2"/>
-        <v>146.5999999999998</v>
-      </c>
-      <c r="W7">
-        <f>+W5-W6</f>
-        <v>384.5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="K8" s="1">
-        <f>-0.5+2.4</f>
-        <v>1.9</v>
-      </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="O8" s="1">
-        <f>-0.5+16.9</f>
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1">
-        <v>-5.4</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1">
-        <f>-5-14.8</f>
-        <v>-19.8</v>
-      </c>
-      <c r="O9" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="U9">
-        <v>-3</v>
-      </c>
-      <c r="V9">
-        <v>-1.2</v>
-      </c>
-      <c r="W9">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1">
-        <f>+J7+J8+J9</f>
-        <v>70.19999999999996</v>
-      </c>
-      <c r="K10" s="1">
-        <f>+K7+K8+K9</f>
-        <v>78.300000000000011</v>
-      </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1">
-        <f>+N7+N8+N9</f>
-        <v>85.100000000000009</v>
-      </c>
-      <c r="O10" s="1">
-        <f>+O7+O8+O9</f>
-        <v>116.39999999999999</v>
-      </c>
-      <c r="U10">
-        <f t="shared" ref="U10:V10" si="3">+U7+U9</f>
-        <v>52.39999999999992</v>
-      </c>
-      <c r="V10">
-        <f t="shared" si="3"/>
-        <v>145.39999999999981</v>
-      </c>
-      <c r="W10">
-        <f>+W7+W9</f>
-        <v>394.9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1">
-        <v>14.8</v>
-      </c>
-      <c r="K11" s="1">
-        <v>-28.4</v>
-      </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1">
-        <v>21.3</v>
-      </c>
-      <c r="O11" s="1">
-        <v>21.3</v>
-      </c>
-      <c r="U11">
-        <v>12.8</v>
-      </c>
-      <c r="V11">
-        <v>38.799999999999997</v>
-      </c>
-      <c r="W11">
-        <v>96.8</v>
-      </c>
-    </row>
-    <row r="12" spans="2:48" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5">
-        <f>+J10+J11</f>
-        <v>84.999999999999957</v>
-      </c>
-      <c r="K12" s="5">
-        <f>+K10+K11</f>
-        <v>49.900000000000013</v>
-      </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5">
-        <f>+N10+N11</f>
-        <v>106.4</v>
-      </c>
-      <c r="O12" s="5">
-        <f>+O10+O11</f>
-        <v>137.69999999999999</v>
-      </c>
-      <c r="Q12" s="4">
-        <v>-13.8</v>
-      </c>
-      <c r="R12" s="4">
-        <v>33.5</v>
-      </c>
-      <c r="S12" s="4">
-        <v>40.6</v>
-      </c>
-      <c r="T12" s="4">
-        <v>68.7</v>
-      </c>
-      <c r="U12" s="4">
-        <f t="shared" ref="U12:V12" si="4">+U10-U11</f>
-        <v>39.599999999999923</v>
-      </c>
-      <c r="V12" s="4">
-        <f t="shared" si="4"/>
-        <v>106.59999999999981</v>
-      </c>
-      <c r="W12" s="4">
-        <f>+W10-W11</f>
-        <v>298.09999999999997</v>
-      </c>
-      <c r="X12" s="4">
-        <f>+W12*1.1</f>
-        <v>327.90999999999997</v>
-      </c>
-      <c r="Y12" s="4">
-        <f t="shared" ref="Y12:AD12" si="5">+X12*1.1</f>
-        <v>360.70100000000002</v>
-      </c>
-      <c r="Z12" s="4">
-        <f t="shared" si="5"/>
-        <v>396.77110000000005</v>
-      </c>
-      <c r="AA12" s="4">
-        <f t="shared" si="5"/>
-        <v>436.44821000000007</v>
-      </c>
-      <c r="AB12" s="4">
-        <f t="shared" si="5"/>
-        <v>480.09303100000011</v>
-      </c>
-      <c r="AC12" s="4">
-        <f t="shared" si="5"/>
-        <v>528.10233410000012</v>
-      </c>
-      <c r="AD12" s="4">
-        <f t="shared" si="5"/>
-        <v>580.91256751000014</v>
-      </c>
-      <c r="AE12" s="4">
-        <f>+AD12*0.97</f>
-        <v>563.48519048470007</v>
-      </c>
-      <c r="AF12" s="4">
-        <f t="shared" ref="AF12:AV12" si="6">+AE12*0.97</f>
-        <v>546.58063477015901</v>
-      </c>
-      <c r="AG12" s="4">
-        <f t="shared" si="6"/>
-        <v>530.18321572705418</v>
-      </c>
-      <c r="AH12" s="4">
-        <f t="shared" si="6"/>
-        <v>514.27771925524257</v>
-      </c>
-      <c r="AI12" s="4">
-        <f t="shared" si="6"/>
-        <v>498.8493876775853</v>
-      </c>
-      <c r="AJ12" s="4">
-        <f t="shared" si="6"/>
-        <v>483.88390604725771</v>
-      </c>
-      <c r="AK12" s="4">
-        <f t="shared" si="6"/>
-        <v>469.36738886583998</v>
-      </c>
-      <c r="AL12" s="4">
-        <f t="shared" si="6"/>
-        <v>455.2863671998648</v>
-      </c>
-      <c r="AM12" s="4">
-        <f t="shared" si="6"/>
-        <v>441.62777618386883</v>
-      </c>
-      <c r="AN12" s="4">
-        <f t="shared" si="6"/>
-        <v>428.37894289835276</v>
-      </c>
-      <c r="AO12" s="4">
-        <f t="shared" si="6"/>
-        <v>415.52757461140214</v>
-      </c>
-      <c r="AP12" s="4">
-        <f t="shared" si="6"/>
-        <v>403.06174737306009</v>
-      </c>
-      <c r="AQ12" s="4">
-        <f t="shared" si="6"/>
-        <v>390.9698949518683</v>
-      </c>
-      <c r="AR12" s="4">
-        <f t="shared" si="6"/>
-        <v>379.24079810331222</v>
-      </c>
-      <c r="AS12" s="4">
-        <f t="shared" si="6"/>
-        <v>367.86357416021286</v>
-      </c>
-      <c r="AT12" s="4">
-        <f t="shared" si="6"/>
-        <v>356.82766693540646</v>
-      </c>
-      <c r="AU12" s="4">
-        <f t="shared" si="6"/>
-        <v>346.12283692734422</v>
-      </c>
-      <c r="AV12" s="4">
-        <f t="shared" si="6"/>
-        <v>335.7391518195239</v>
-      </c>
-    </row>
-    <row r="13" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>29</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -1274,28 +957,49 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="1">
-        <f>+J12/J14</f>
-        <v>4.2812531479802542</v>
-      </c>
       <c r="K13" s="1">
-        <f>+K12/K14</f>
-        <v>2.4962481240620318</v>
-      </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
+        <f>+K11-K12</f>
+        <v>186.39999999999998</v>
+      </c>
+      <c r="L13" s="1">
+        <f>+L11-L12</f>
+        <v>178</v>
+      </c>
+      <c r="M13" s="1">
+        <f>+M11-M12</f>
+        <v>240</v>
+      </c>
       <c r="N13" s="1">
-        <f>+N12/N14</f>
-        <v>5.3591215875894029</v>
+        <v>104.3</v>
       </c>
       <c r="O13" s="1">
-        <f>+O12/O14</f>
-        <v>6.9241212852617284</v>
-      </c>
-    </row>
-    <row r="14" spans="2:48" x14ac:dyDescent="0.2">
+        <f>+O11-O12</f>
+        <v>233</v>
+      </c>
+      <c r="P13" s="1">
+        <f>+P11-P12</f>
+        <v>220</v>
+      </c>
+      <c r="Q13" s="1">
+        <f>+Q11-Q12</f>
+        <v>341</v>
+      </c>
+      <c r="U13">
+        <f t="shared" ref="U13:V13" si="1">+U11-U12</f>
+        <v>318.09999999999991</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="1"/>
+        <v>445.19999999999982</v>
+      </c>
+      <c r="W13">
+        <f>+W11-W12</f>
+        <v>859.5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -1304,390 +1008,954 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
+        <v>110.9</v>
+      </c>
+      <c r="L14" s="1">
+        <v>103</v>
+      </c>
+      <c r="M14" s="1">
+        <v>127</v>
+      </c>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1">
+        <v>128.6</v>
+      </c>
+      <c r="P14" s="1">
+        <v>121.8</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>162</v>
+      </c>
+      <c r="U14">
+        <v>262.7</v>
+      </c>
+      <c r="V14">
+        <v>298.60000000000002</v>
+      </c>
+      <c r="W14">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="15" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="K15" s="1">
+        <f>+K13-K14</f>
+        <v>75.499999999999972</v>
+      </c>
+      <c r="L15" s="1">
+        <f>+L13-L14</f>
+        <v>75</v>
+      </c>
+      <c r="M15" s="1">
+        <f>+M13-M14</f>
+        <v>113</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1">
+        <f>+O13-O14</f>
+        <v>104.4</v>
+      </c>
+      <c r="P15" s="1">
+        <f>+P13-P14</f>
+        <v>98.2</v>
+      </c>
+      <c r="Q15" s="1">
+        <f>+Q13-Q14</f>
+        <v>179</v>
+      </c>
+      <c r="U15">
+        <f t="shared" ref="U15:V15" si="2">+U13-U14</f>
+        <v>55.39999999999992</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="2"/>
+        <v>146.5999999999998</v>
+      </c>
+      <c r="W15">
+        <f>+W13-W14</f>
+        <v>384.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="K16" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="L16" s="1">
+        <f>-0.5+2.4</f>
+        <v>1.9</v>
+      </c>
+      <c r="M16" s="1">
+        <v>-0.53400000000000003</v>
+      </c>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="P16" s="1">
+        <f>-0.5+16.9</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="17" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="K17" s="1">
+        <v>-5.4</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1">
+        <f>-5-14.8</f>
+        <v>-19.8</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>-0.18099999999999999</v>
+      </c>
+      <c r="U17">
+        <v>-3</v>
+      </c>
+      <c r="V17">
+        <v>-1.2</v>
+      </c>
+      <c r="W17">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1">
+        <f>+K15+K16+K17</f>
+        <v>70.19999999999996</v>
+      </c>
+      <c r="L18" s="1">
+        <f>+L15+L16+L17</f>
+        <v>78.300000000000011</v>
+      </c>
+      <c r="M18" s="1">
+        <f>+M15+M16+M17</f>
+        <v>113.16</v>
+      </c>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1">
+        <f>+O15+O16+O17</f>
+        <v>85.100000000000009</v>
+      </c>
+      <c r="P18" s="1">
+        <f>+P15+P16+P17</f>
+        <v>116.39999999999999</v>
+      </c>
+      <c r="Q18" s="1">
+        <f>+Q15+Q16+Q17</f>
+        <v>178.94799999999998</v>
+      </c>
+      <c r="U18">
+        <f t="shared" ref="U18:V18" si="3">+U15+U17</f>
+        <v>52.39999999999992</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="3"/>
+        <v>145.39999999999981</v>
+      </c>
+      <c r="W18">
+        <f>+W15+W17</f>
+        <v>394.9</v>
+      </c>
+    </row>
+    <row r="19" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="L19" s="1">
+        <v>-28.4</v>
+      </c>
+      <c r="M19" s="1">
+        <v>-29.5</v>
+      </c>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1">
+        <v>21.3</v>
+      </c>
+      <c r="P19" s="1">
+        <v>21.3</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>51.292999999999999</v>
+      </c>
+      <c r="U19">
+        <v>12.8</v>
+      </c>
+      <c r="V19">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="W19">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:48" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="K20" s="4">
+        <f>+K18+K19</f>
+        <v>84.999999999999957</v>
+      </c>
+      <c r="L20" s="4">
+        <f>+L18+L19</f>
+        <v>49.900000000000013</v>
+      </c>
+      <c r="M20" s="4">
+        <f>+M18+M19</f>
+        <v>83.66</v>
+      </c>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4">
+        <f>+O18+O19</f>
+        <v>106.4</v>
+      </c>
+      <c r="P20" s="4">
+        <f>+P18+P19</f>
+        <v>137.69999999999999</v>
+      </c>
+      <c r="Q20" s="4">
+        <f>+Q18+Q19</f>
+        <v>230.24099999999999</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U20" s="3">
+        <f t="shared" ref="U20:V20" si="4">+U18-U19</f>
+        <v>39.599999999999923</v>
+      </c>
+      <c r="V20" s="3">
+        <f t="shared" si="4"/>
+        <v>106.59999999999981</v>
+      </c>
+      <c r="W20" s="3">
+        <f>+W18-W19</f>
+        <v>298.09999999999997</v>
+      </c>
+      <c r="X20" s="3">
+        <f>+W20*1.1</f>
+        <v>327.90999999999997</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" ref="Y20:AD20" si="5">+X20*1.1</f>
+        <v>360.70100000000002</v>
+      </c>
+      <c r="Z20" s="3">
+        <f t="shared" si="5"/>
+        <v>396.77110000000005</v>
+      </c>
+      <c r="AA20" s="3">
+        <f t="shared" si="5"/>
+        <v>436.44821000000007</v>
+      </c>
+      <c r="AB20" s="3">
+        <f t="shared" si="5"/>
+        <v>480.09303100000011</v>
+      </c>
+      <c r="AC20" s="3">
+        <f t="shared" si="5"/>
+        <v>528.10233410000012</v>
+      </c>
+      <c r="AD20" s="3">
+        <f t="shared" si="5"/>
+        <v>580.91256751000014</v>
+      </c>
+      <c r="AE20" s="3">
+        <f>+AD20*0.97</f>
+        <v>563.48519048470007</v>
+      </c>
+      <c r="AF20" s="3">
+        <f t="shared" ref="AF20:AV20" si="6">+AE20*0.97</f>
+        <v>546.58063477015901</v>
+      </c>
+      <c r="AG20" s="3">
+        <f t="shared" si="6"/>
+        <v>530.18321572705418</v>
+      </c>
+      <c r="AH20" s="3">
+        <f t="shared" si="6"/>
+        <v>514.27771925524257</v>
+      </c>
+      <c r="AI20" s="3">
+        <f t="shared" si="6"/>
+        <v>498.8493876775853</v>
+      </c>
+      <c r="AJ20" s="3">
+        <f t="shared" si="6"/>
+        <v>483.88390604725771</v>
+      </c>
+      <c r="AK20" s="3">
+        <f t="shared" si="6"/>
+        <v>469.36738886583998</v>
+      </c>
+      <c r="AL20" s="3">
+        <f t="shared" si="6"/>
+        <v>455.2863671998648</v>
+      </c>
+      <c r="AM20" s="3">
+        <f t="shared" si="6"/>
+        <v>441.62777618386883</v>
+      </c>
+      <c r="AN20" s="3">
+        <f t="shared" si="6"/>
+        <v>428.37894289835276</v>
+      </c>
+      <c r="AO20" s="3">
+        <f t="shared" si="6"/>
+        <v>415.52757461140214</v>
+      </c>
+      <c r="AP20" s="3">
+        <f t="shared" si="6"/>
+        <v>403.06174737306009</v>
+      </c>
+      <c r="AQ20" s="3">
+        <f t="shared" si="6"/>
+        <v>390.9698949518683</v>
+      </c>
+      <c r="AR20" s="3">
+        <f t="shared" si="6"/>
+        <v>379.24079810331222</v>
+      </c>
+      <c r="AS20" s="3">
+        <f t="shared" si="6"/>
+        <v>367.86357416021286</v>
+      </c>
+      <c r="AT20" s="3">
+        <f t="shared" si="6"/>
+        <v>356.82766693540646</v>
+      </c>
+      <c r="AU20" s="3">
+        <f t="shared" si="6"/>
+        <v>346.12283692734422</v>
+      </c>
+      <c r="AV20" s="3">
+        <f t="shared" si="6"/>
+        <v>335.7391518195239</v>
+      </c>
+    </row>
+    <row r="21" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1">
+        <f>+K20/K22</f>
+        <v>4.2812531479802542</v>
+      </c>
+      <c r="L21" s="1">
+        <f>+L20/L22</f>
+        <v>2.4962481240620318</v>
+      </c>
+      <c r="M21" s="1">
+        <f>+M20/M22</f>
+        <v>4.2132746959917835</v>
+      </c>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1">
+        <f>+O20/O22</f>
+        <v>5.3591215875894029</v>
+      </c>
+      <c r="P21" s="1">
+        <f>+P20/P22</f>
+        <v>6.9241212852617284</v>
+      </c>
+      <c r="Q21" s="1">
+        <f>+Q20/Q22</f>
+        <v>11.555962658100782</v>
+      </c>
+    </row>
+    <row r="22" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="K22" s="1">
         <v>19.853999999999999</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L22" s="1">
         <v>19.989999999999998</v>
       </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1">
+      <c r="M22" s="1">
+        <v>19.856289</v>
+      </c>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1">
         <v>19.853999999999999</v>
       </c>
-      <c r="O14" s="1">
+      <c r="P22" s="1">
         <v>19.887</v>
       </c>
-    </row>
-    <row r="16" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
+      <c r="Q22" s="1">
+        <v>19.923999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
         <v>31</v>
       </c>
-      <c r="N16" s="2" t="e">
-        <f>+N3/M3-1</f>
+      <c r="O24" s="2">
+        <f>+O11/N11-1</f>
+        <v>8.918617614268598E-4</v>
+      </c>
+      <c r="P24" s="2">
+        <f>+P11/O11-1</f>
+        <v>-2.9850746268656692E-2</v>
+      </c>
+      <c r="Q24" s="2">
+        <f>+Q11/P11-1</f>
+        <v>0.42709529276693448</v>
+      </c>
+      <c r="X24" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y24" s="5">
+        <f>+NPV(0.08,X20:AV20)</f>
+        <v>4803.8113977917474</v>
+      </c>
+    </row>
+    <row r="25" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="O25" s="2">
+        <f>+O13/O11</f>
+        <v>0.25952327912675432</v>
+      </c>
+      <c r="P25" s="2">
+        <f>+P13/P11</f>
+        <v>0.2525832376578645</v>
+      </c>
+      <c r="Q25" s="2">
+        <f>+Q13/Q11</f>
+        <v>0.27433628318584069</v>
+      </c>
+      <c r="X25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y25" s="1">
+        <f>+Y24-main!L6+main!L7</f>
+        <v>4608.8113977917474</v>
+      </c>
+    </row>
+    <row r="26" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="O26" s="2">
+        <f>+O16/O11</f>
+        <v>5.5691690799732681E-4</v>
+      </c>
+      <c r="P26" s="2">
+        <f>+P16/P11</f>
+        <v>1.8828932261768083E-2</v>
+      </c>
+      <c r="Q26" s="2">
+        <f>+Q16/Q11</f>
+        <v>1.0378117457763475E-4</v>
+      </c>
+      <c r="X26" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y26">
+        <f>+Y25/main!L4</f>
+        <v>231.24994469602345</v>
+      </c>
+    </row>
+    <row r="27" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="O27" s="2">
+        <f>+O19/O18</f>
+        <v>0.25029377203290243</v>
+      </c>
+      <c r="P27" s="2">
+        <f>+P19/P18</f>
+        <v>0.1829896907216495</v>
+      </c>
+      <c r="Q27" s="2">
+        <f>+Q19/Q18</f>
+        <v>0.28663634128350141</v>
+      </c>
+    </row>
+    <row r="28" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="O28" s="2" t="e">
+        <f>+O20/N20-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O16" s="2">
-        <f>+O3/N3-1</f>
-        <v>-2.9850746268656692E-2</v>
-      </c>
-      <c r="Y16" s="6">
-        <f>+NPV(0.08,X12:AV12)</f>
-        <v>4803.8113977917474</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="N17" s="2">
-        <f>+N5/N3</f>
-        <v>0.25952327912675432</v>
-      </c>
-      <c r="O17" s="2">
-        <f>+O5/O3</f>
-        <v>0.2525832376578645</v>
-      </c>
-      <c r="Y17" s="1">
-        <f>+Y16-main!L6+main!L7</f>
-        <v>4608.8113977917474</v>
-      </c>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="N18" s="2">
-        <f>+N8/N3</f>
-        <v>5.5691690799732681E-4</v>
-      </c>
-      <c r="O18" s="2">
-        <f>+O8/O3</f>
-        <v>1.8828932261768083E-2</v>
-      </c>
-      <c r="Y18">
-        <f>+Y17/main!L4</f>
-        <v>231.24994469602345</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="N19" s="2">
-        <f>+N11/N10</f>
-        <v>0.25029377203290243</v>
-      </c>
-      <c r="O19" s="2">
-        <f>+O11/O10</f>
-        <v>0.1829896907216495</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="N20" s="2" t="e">
-        <f>+N12/M12-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O20" s="2">
-        <f>+O12/N12-1</f>
+      <c r="P28" s="2">
+        <f>+P20/O20-1</f>
         <v>0.29417293233082686</v>
       </c>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
+      <c r="Q28" s="2">
+        <f>+Q20/P20-1</f>
+        <v>0.67204793028322451</v>
+      </c>
+    </row>
+    <row r="29" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
         <v>36</v>
       </c>
-      <c r="N21" s="2">
-        <f>((N14-M14)*100)</f>
-        <v>1985.3999999999999</v>
-      </c>
-      <c r="O21" s="2">
-        <f>((O14-N14)*100)</f>
-        <v>3.3000000000001251</v>
-      </c>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
+      <c r="O29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" s="2">
+        <f>((P22-O22))</f>
+        <v>3.3000000000001251E-2</v>
+      </c>
+      <c r="Q29" s="2">
+        <f>((Q22-P22))</f>
+        <v>3.6999999999999034E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
         <v>3</v>
       </c>
-      <c r="O23">
+      <c r="P31">
         <f>88.8+169.9+85.8+63.9</f>
         <v>408.4</v>
       </c>
     </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
+    <row r="32" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="O24">
+      <c r="P32">
         <v>524.4</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
         <v>38</v>
       </c>
-      <c r="O25">
+      <c r="P33">
         <v>104.5</v>
       </c>
     </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
         <v>39</v>
       </c>
-      <c r="O26">
+      <c r="P34">
         <v>110.4</v>
       </c>
     </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
         <v>40</v>
       </c>
-      <c r="O27">
+      <c r="P35">
         <v>25.9</v>
       </c>
     </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
         <v>41</v>
       </c>
-      <c r="O28">
+      <c r="P36">
         <v>220.3</v>
       </c>
     </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
         <v>42</v>
       </c>
-      <c r="O29">
+      <c r="P37">
         <f>107.8+38.2</f>
         <v>146</v>
       </c>
     </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
         <v>43</v>
       </c>
-      <c r="O30">
+      <c r="P38">
         <v>14.3</v>
       </c>
     </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
         <v>44</v>
       </c>
-      <c r="O31">
+      <c r="P39">
         <v>91.4</v>
       </c>
     </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
         <v>45</v>
       </c>
-      <c r="O32">
+      <c r="P40">
         <v>12.7</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
         <v>46</v>
       </c>
-      <c r="O33">
-        <f>SUM(O23:O32)</f>
+      <c r="P41">
+        <f>SUM(P31:P40)</f>
         <v>1658.3000000000002</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
         <v>4</v>
       </c>
-      <c r="O35">
+      <c r="P43">
         <v>212.6</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
         <v>47</v>
       </c>
-      <c r="O36">
+      <c r="P44">
         <v>403</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
         <v>48</v>
       </c>
-      <c r="O37">
+      <c r="P45">
         <v>65.8</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
         <v>27</v>
       </c>
-      <c r="O38">
+      <c r="P46">
         <v>6.8</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
         <v>49</v>
       </c>
-      <c r="O39">
+      <c r="P47">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
         <v>50</v>
       </c>
-      <c r="O40">
-        <f>SUM(O35:O39)</f>
+      <c r="P48">
+        <f>SUM(P43:P47)</f>
         <v>693.19999999999993</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
         <v>52</v>
       </c>
-      <c r="O42">
-        <f>+O33-O40</f>
+      <c r="P50">
+        <f>+P41-P48</f>
         <v>965.10000000000025</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
         <v>51</v>
       </c>
-      <c r="O43">
-        <f>+O40+O42</f>
+      <c r="P51">
+        <f>+P48+P50</f>
         <v>1658.3000000000002</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
         <v>53</v>
       </c>
-      <c r="O45" s="3">
-        <f>+O12/O33</f>
+      <c r="P53" s="2">
+        <f>+P20/P41</f>
         <v>8.3036844961707754E-2</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
         <v>54</v>
       </c>
-      <c r="O46" s="3">
-        <f>+O12/O42</f>
+      <c r="P54" s="2">
+        <f>+P20/P50</f>
         <v>0.14267951507615786</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
         <v>62</v>
       </c>
-      <c r="K48" s="1">
-        <f>+K12</f>
+      <c r="L56" s="1">
+        <f>+L20</f>
         <v>49.900000000000013</v>
       </c>
-      <c r="O48" s="1">
-        <f>+O12</f>
+      <c r="P56" s="1">
+        <f>+P20</f>
         <v>137.69999999999999</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B49" t="s">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
         <v>63</v>
       </c>
-      <c r="J49">
+      <c r="K57">
         <v>57.7</v>
       </c>
-      <c r="N49">
+      <c r="O57">
         <v>91.8</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
         <v>55</v>
       </c>
-      <c r="J50">
+      <c r="J58">
         <v>37.299999999999997</v>
       </c>
-      <c r="N50">
+      <c r="N58">
         <v>27.7</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
         <v>61</v>
       </c>
-      <c r="J51">
+      <c r="J59">
         <v>2</v>
       </c>
-      <c r="N51">
+      <c r="N59">
         <v>3.8</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
         <v>56</v>
       </c>
-      <c r="J52">
+      <c r="J60">
         <v>-58.4</v>
       </c>
-      <c r="N52">
+      <c r="N60">
         <v>-46.2</v>
       </c>
     </row>
-    <row r="53" spans="2:14" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="B53" s="4" t="s">
+    <row r="61" spans="2:16" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="B61" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J53" s="4">
+      <c r="J61" s="3">
         <v>-13.2</v>
       </c>
-      <c r="N53" s="4">
+      <c r="N61" s="3">
         <v>-46.6</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B54" t="s">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B62" t="s">
         <v>57</v>
       </c>
-      <c r="J54">
+      <c r="J62">
         <v>20.6</v>
       </c>
-      <c r="N54">
+      <c r="N62">
         <v>-19.8</v>
       </c>
     </row>
-    <row r="55" spans="2:14" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="B55" s="4" t="s">
+    <row r="63" spans="2:16" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="B63" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J55" s="4">
-        <f>+J50+J52+J54</f>
+      <c r="J63" s="3">
+        <f>+J58+J60+J62</f>
         <v>-0.5</v>
       </c>
-      <c r="N55" s="4">
-        <f>+N50+N52+N54</f>
+      <c r="N63" s="3">
+        <f>+N58+N60+N62</f>
         <v>-38.300000000000004</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B64" t="s">
         <v>59</v>
       </c>
-      <c r="J56">
-        <f>+J50-J51+J53</f>
+      <c r="J64">
+        <f>+J58-J59+J61</f>
         <v>22.099999999999998</v>
       </c>
-      <c r="N56">
-        <f>+N50-N51+N53</f>
+      <c r="N64">
+        <f>+N58-N59+N61</f>
         <v>-22.700000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67E6059-CA68-490D-83DC-9C0B775FE01B}">
+  <dimension ref="B2:B15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
